--- a/exam/spreadsheets.xlsx
+++ b/exam/spreadsheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scunning/St-Gallen/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA8B5DE-1702-8F49-8935-D32E32443D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FF0014-5C84-5B4E-B452-2980D204E835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20360" activeTab="2" xr2:uid="{7EEA2DF3-D38D-214E-8F48-4BAA6627C176}"/>
   </bookViews>
